--- a/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2218,6 +2218,33 @@
       <c r="E39" s="20" t="inlineStr">
         <is>
           <t>비밀번호를 자주 잊는다면 앱 패스키 등록을 권합니다. 얼굴만 보면 들어가져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="54" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>학부모 월간 성적표 (내 평가가 반영돼요)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>평소처럼 수업 평가서를 성실히 작성해요. → 발음 연습·판단력 훈련 기록이 자동으로 축에 반영돼요. → 성적표의 담임의 한마디 AI 초안을 확인하고 다듬어요. → 미리보기로 오각형이 잘 채워졌는지 확인해요.</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>매 수업 한 줄이라도 평가를 남기면 월말 성적표가 저절로 완성됩니다.</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F424"/>
+  <dimension ref="A1:F435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6941,10 +6968,131 @@
       <c r="E424" s="33" t="n"/>
       <c r="F424" s="33" t="n"/>
     </row>
+    <row r="426" ht="26" customHeight="1">
+      <c r="A426" s="21" t="inlineStr">
+        <is>
+          <t>37  🌟 학부모 월간 성적표 (내 평가가 반영돼요)  —  오각형 5축은 내가 남긴 평가로 채워져요</t>
+        </is>
+      </c>
+      <c r="B426" s="22" t="n"/>
+      <c r="C426" s="22" t="n"/>
+      <c r="D426" s="22" t="n"/>
+      <c r="E426" s="22" t="n"/>
+      <c r="F426" s="22" t="n"/>
+    </row>
+    <row r="427" ht="42" customHeight="1">
+      <c r="A427" s="23" t="inlineStr">
+        <is>
+          <t>📖 학부모에게 나가는 오각형 월간 성적표의 다섯 축(발음·유창성 / 어휘 / 문장 구성력 / 수업 태도 / 참여도)은 선생님이 남긴 수업 평가와 발음 기록으로 채워집니다. 평가를 꾸준히 남길수록 성적표가 정확하고 풍성해져요. 담임의 한마디는 AI 초안을 확인·수정해 내보냅니다.</t>
+        </is>
+      </c>
+      <c r="B427" s="24" t="n"/>
+      <c r="C427" s="24" t="n"/>
+      <c r="D427" s="24" t="n"/>
+      <c r="E427" s="24" t="n"/>
+      <c r="F427" s="24" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B428" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="30" customHeight="1">
+      <c r="A429" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B429" s="28" t="inlineStr">
+        <is>
+          <t>평소처럼 수업 평가서를 성실히 작성해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="30" customHeight="1">
+      <c r="A430" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>발음 연습·판단력 훈련 기록이 자동으로 축에 반영돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="30" customHeight="1">
+      <c r="A431" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B431" s="28" t="inlineStr">
+        <is>
+          <t>성적표의 담임의 한마디 AI 초안을 확인하고 다듬어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="30" customHeight="1">
+      <c r="A432" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B432" s="28" t="inlineStr">
+        <is>
+          <t>미리보기로 오각형이 잘 채워졌는지 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B433" s="30" t="inlineStr">
+        <is>
+          <t>값이 있는 축만 채워져요 — 평가가 없으면 그 축은 비어 보여요.</t>
+        </is>
+      </c>
+      <c r="C433" s="31" t="n"/>
+      <c r="D433" s="31" t="n"/>
+      <c r="E433" s="31" t="n"/>
+      <c r="F433" s="31" t="n"/>
+    </row>
+    <row r="434" ht="24" customHeight="1">
+      <c r="A434" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B434" s="30" t="inlineStr">
+        <is>
+          <t>긴 코멘트보다 꾸준한 평가가 성적표 품질을 좌우해요.</t>
+        </is>
+      </c>
+      <c r="C434" s="31" t="n"/>
+      <c r="D434" s="31" t="n"/>
+      <c r="E434" s="31" t="n"/>
+      <c r="F434" s="31" t="n"/>
+    </row>
+    <row r="435" ht="30" customHeight="1">
+      <c r="A435" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매 수업 한 줄이라도 평가를 남기면 월말 성적표가 저절로 완성됩니다.</t>
+        </is>
+      </c>
+      <c r="B435" s="33" t="n"/>
+      <c r="C435" s="33" t="n"/>
+      <c r="D435" s="33" t="n"/>
+      <c r="E435" s="33" t="n"/>
+      <c r="F435" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="388">
+  <mergeCells count="398">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B432:F432"/>
     <mergeCell ref="B276:F276"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
@@ -6971,6 +7119,7 @@
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B433:F433"/>
     <mergeCell ref="B233:F233"/>
     <mergeCell ref="B420:F420"/>
     <mergeCell ref="B224:F224"/>
@@ -6987,6 +7136,7 @@
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A435:F435"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
     <mergeCell ref="B317:F317"/>
@@ -7100,6 +7250,7 @@
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A402:F402"/>
     <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B428:F428"/>
     <mergeCell ref="B284:F284"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="B344:F344"/>
@@ -7109,6 +7260,7 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A426:F426"/>
     <mergeCell ref="A364:F364"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="B297:F297"/>
@@ -7130,9 +7282,11 @@
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B429:F429"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B294:F294"/>
     <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B431:F431"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B287:F287"/>
@@ -7142,6 +7296,7 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="B241:F241"/>
     <mergeCell ref="A260:F260"/>
+    <mergeCell ref="B434:F434"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="B80:F80"/>
@@ -7200,6 +7355,7 @@
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B334:F334"/>
+    <mergeCell ref="A427:F427"/>
     <mergeCell ref="B309:F309"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B380:F380"/>
@@ -7318,6 +7474,7 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B430:F430"/>
     <mergeCell ref="B417:F417"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B196:F196"/>
